--- a/output/2026-09-05_15_Italia_Sicilia_ATEX_Equipment_Services.xlsx
+++ b/output/2026-09-05_15_Italia_Sicilia_ATEX_Equipment_Services.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Confermato su LinkedIn, Facebook, PagineBianche, PagineGialle, sito ufficiale. Ha anche attivita accessoria di taglio lamiera.</t>
+          <t>Confermato su LinkedIn, Facebook, PagineBianche, PagineGialle, sito ufficiale. Ha anche attivita accessoria di taglio lamiera. [DUPLICATO — vedi anche: 2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -542,7 +542,6 @@
           <t>Trincair Condotti S.r.l.s.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Cortile Patania 3, 90121 Palermo (PA)</t>
@@ -560,7 +559,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nessun sito ufficiale rintracciato. Confermato su PagineGialle e Virgilio Aziende.</t>
+          <t>Nessun sito ufficiale rintracciato. Confermato su PagineGialle e Virgilio Aziende. [DUPLICATO — vedi anche: 2026-09-05_13_Italia_Sicilia_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -612,7 +611,6 @@
           <t>Pitti S.r.l. Impianti Aeraulici Palermo</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Via Arena Oreste 16/A, 90142 Palermo (PA)</t>
@@ -667,7 +665,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Confermato su sito ufficiale, Virgilio Aziende, GuidaSicilia, PagineGialle. Email non reperita.</t>
+          <t>Confermato su sito ufficiale, Virgilio Aziende, GuidaSicilia, PagineGialle. Email non reperita. [DUPLICATO — vedi anche: 2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
